--- a/routing/taskana-routing-rest/src/test/resources/testExcelRouting.xlsx
+++ b/routing/taskana-routing-rest/src/test/resources/testExcelRouting.xlsx
@@ -1,22 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24617"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23C49DF8-144B-4E51-B7A1-209A8A3AFCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="5790"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="5790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="workbasketRouting" sheetId="1" r:id="rId1"/>
     <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
     <sheet name="Tabelle3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Input</t>
   </si>
@@ -24,71 +36,65 @@
     <t>Output</t>
   </si>
   <si>
+    <t>BKN</t>
+  </si>
+  <si>
+    <t>ClassificationKey</t>
+  </si>
+  <si>
+    <t>workbasketKey</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>JUEL</t>
+  </si>
+  <si>
+    <t>javascript</t>
+  </si>
+  <si>
     <t>Expression</t>
   </si>
   <si>
+    <t>task.primaryObjRef.value</t>
+  </si>
+  <si>
+    <t>task.classificationSummary.key + task.note</t>
+  </si>
+  <si>
     <t>FIRST</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>javascript</t>
-  </si>
-  <si>
-    <t>task.primaryObjRef.value</t>
-  </si>
-  <si>
-    <t>task.classificationSummary.key + task.note</t>
-  </si>
-  <si>
     <t>06260203</t>
   </si>
   <si>
-    <t>GPK_ARS</t>
-  </si>
-  <si>
-    <t>ULAK-D</t>
+    <t>GPK_KSC</t>
+  </si>
+  <si>
+    <t>DOMAIN_A</t>
   </si>
   <si>
     <t>VIP-Team</t>
   </si>
   <si>
+    <t>matches(cellInput,"11048|12012|12013|12513|12523|12619|12910|12911|12912|12913|12914|12915|12916|12917|12918|12919|12920|12921|12922|12923|12924|12925|12926|12927|12928|12929|12930|12931|12932|12933|12934|13082|13093|17999|19012")</t>
+  </si>
+  <si>
     <t>Second-Level Team 1</t>
   </si>
   <si>
-    <t>GPK_ARS_4</t>
-  </si>
-  <si>
-    <t>JUEL</t>
-  </si>
-  <si>
-    <t>BKN</t>
-  </si>
-  <si>
-    <t>ClassificationKey</t>
-  </si>
-  <si>
-    <t>workbasketKey</t>
-  </si>
-  <si>
-    <t>domain</t>
-  </si>
-  <si>
-    <t>matches(cellInput,"11048|12012|12013|12513|12523|12619|12910|12911|12912|12913|12914|12915|12916|12917|12918|12919|12920|12921|12922|12923|12924|12925|12926|12927|12928|12929|12930|12931|12932|12933|12934|13082|13093|17999|19012")</t>
-  </si>
-  <si>
     <t>12345678</t>
-  </si>
-  <si>
-    <t>GPK_ARS_3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,7 +168,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -178,7 +184,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -253,6 +259,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -288,6 +311,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -463,9 +503,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
@@ -473,7 +513,7 @@
     <col min="6" max="6" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -488,111 +528,111 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="B2" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -601,18 +641,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/routing/taskana-routing-rest/src/test/resources/testExcelRouting.xlsx
+++ b/routing/taskana-routing-rest/src/test/resources/testExcelRouting.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24617"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23C49DF8-144B-4E51-B7A1-209A8A3AFCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A658817E-49CF-4036-81E9-A9EC84A0D901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="5790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
